--- a/step7内容分析和注释模板.xlsx
+++ b/step7内容分析和注释模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22192" windowHeight="10455"/>
+    <workbookView windowWidth="18202" windowHeight="10387"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="159">
   <si>
     <t>模块ID</t>
   </si>
@@ -481,12 +481,6 @@
   </si>
   <si>
     <t>2024年摊销前 CSM 变动项占比</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当期摊销前的CSM变动项目，包括新业务CSM、CSM计息和CSM调整；可以将这三项归纳为Organic growth和Non-organic growth。
-与未来服务相关的履约现金流估计的变化可以被CSM吸收，通常包括非经济假设变化的调整以及适用于VFA模型的金融风险变化的调整等。
-CSM计息的基础包括期初存量的CSM余额和当期新增CSM，它在增加CSM的同时会计入承保财务损益。计息率需采用合同组锁定计息率，不随报告日市场利率曲线波动。
-</t>
   </si>
   <si>
     <t>csm_ratio_trend</t>
@@ -1703,7 +1697,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16317595" y="5757545"/>
+          <a:off x="16317595" y="5767705"/>
           <a:ext cx="9746615" cy="431800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1741,7 +1735,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16565880" y="6929120"/>
+          <a:off x="16565880" y="6939280"/>
           <a:ext cx="9429750" cy="509905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2202,7 +2196,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="27.75" spans="1:19">
+    <row r="9" ht="28.5" spans="1:19">
       <c r="A9" s="5" t="s">
         <v>36</v>
       </c>
@@ -2227,7 +2221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="14.6" spans="1:19">
+    <row r="10" ht="14.65" spans="1:19">
       <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
@@ -2384,7 +2378,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="14" ht="27.75" spans="1:19">
+    <row r="14" ht="28.5" spans="1:19">
       <c r="A14" s="5" t="s">
         <v>57</v>
       </c>
@@ -2428,7 +2422,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" ht="41.65" spans="1:19">
+    <row r="16" ht="42.4" spans="1:19">
       <c r="A16" s="5" t="s">
         <v>64</v>
       </c>
@@ -2473,7 +2467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" ht="27.75" spans="1:10">
+    <row r="18" ht="28.5" spans="1:10">
       <c r="A18" s="5" t="s">
         <v>71</v>
       </c>
@@ -2555,7 +2549,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" ht="27.75" spans="1:10">
+    <row r="22" ht="28.5" spans="1:10">
       <c r="A22" s="5" t="s">
         <v>85</v>
       </c>
@@ -2580,7 +2574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" ht="27.75" spans="1:10">
+    <row r="23" ht="28.5" spans="1:10">
       <c r="A23" s="5" t="s">
         <v>87</v>
       </c>
@@ -2622,7 +2616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" ht="27.75" spans="1:10">
+    <row r="25" ht="28.5" spans="1:10">
       <c r="A25" s="5" t="s">
         <v>93</v>
       </c>
@@ -2727,7 +2721,7 @@
       </c>
       <c r="J29" s="11"/>
     </row>
-    <row r="30" ht="195" spans="1:10">
+    <row r="30" ht="181.15" spans="1:10">
       <c r="A30" s="5" t="s">
         <v>109</v>
       </c>
@@ -2741,7 +2735,7 @@
         <v>110</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
@@ -2751,9 +2745,9 @@
       </c>
       <c r="J30" s="11"/>
     </row>
-    <row r="31" ht="75" spans="1:10">
+    <row r="31" ht="75.75" spans="1:10">
       <c r="A31" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
@@ -2762,37 +2756,37 @@
         <v>94</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H31" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="I31" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="32" ht="28.5" spans="1:10">
       <c r="A32" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="D32" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="8" t="s">
@@ -2801,39 +2795,39 @@
     </row>
     <row r="33" ht="70.15" spans="1:9">
       <c r="A33" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>121</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" ht="27.75" spans="1:9">
+    <row r="34" ht="28.5" spans="1:9">
       <c r="A34" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>125</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -2845,23 +2839,23 @@
     </row>
     <row r="35" ht="42.4" spans="1:9">
       <c r="A35" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="7" t="s">
+      <c r="E35" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="8" t="s">
@@ -2870,23 +2864,23 @@
     </row>
     <row r="36" ht="111.75" spans="1:9">
       <c r="A36" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="E36" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="10" t="s">
@@ -2895,42 +2889,42 @@
     </row>
     <row r="37" ht="42.4" spans="1:9">
       <c r="A37" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" ht="152.65" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" ht="153.4" spans="1:9">
       <c r="A38" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -2939,17 +2933,17 @@
     </row>
     <row r="39" ht="305.65" spans="1:9">
       <c r="A39" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
@@ -2958,17 +2952,17 @@
     </row>
     <row r="40" ht="125.65" spans="1:9">
       <c r="A40" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
@@ -2977,17 +2971,17 @@
     </row>
     <row r="41" ht="42.4" spans="1:9">
       <c r="A41" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
@@ -2996,17 +2990,17 @@
     </row>
     <row r="42" ht="28.5" spans="1:9">
       <c r="A42" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
@@ -3015,21 +3009,21 @@
     </row>
     <row r="43" ht="54" customHeight="1" spans="1:9">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" s="16" t="s">
         <v>157</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>158</v>
       </c>
       <c r="F43" s="16"/>
       <c r="G43" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
